--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -14724,16 +14724,16 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="O87" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="Q87" t="n">
         <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>0.1782932329888682</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S87" t="inlineStr">
         <is>
@@ -15268,16 +15268,16 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O90" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="Q90" t="n">
         <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>0.01303707733931069</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S90" t="inlineStr">
         <is>
@@ -16700,16 +16700,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="O99" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.003875939847584092</v>
+        <v>0.01162781954275227</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18751</v>
+        <v>18757</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -13044,16 +13044,16 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="O77" t="n">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="Q77" t="n">
         <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1511616540557796</v>
+        <v>0.1472857142081955</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -16700,16 +16700,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="O99" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.01162781954275227</v>
+        <v>0.01356578946654432</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16959,7 +16959,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18757</v>
+        <v>18756</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -16700,16 +16700,16 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="O99" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="Q99" t="n">
         <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>0.01356578946654432</v>
+        <v>0.01744172931412841</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16778,6 +16778,154 @@
       <c r="BC99" t="inlineStr">
         <is>
           <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K100" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N100" t="n">
+        <v>13</v>
+      </c>
+      <c r="O100" t="n">
+        <v>13</v>
+      </c>
+      <c r="Q100" t="n">
+        <v>0</v>
+      </c>
+      <c r="R100" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP100" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR100" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr"/>
+      <c r="AT100" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU100" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16814,7 +16962,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-08-02</t>
         </is>
       </c>
     </row>
@@ -16897,7 +17045,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="10">
@@ -16907,7 +17055,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="11">
@@ -16959,7 +17107,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18756</v>
+        <v>18771</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>9</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -1223,9 +1220,6 @@
       <c r="O5" t="n">
         <v>2</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0.03557618341728275</v>
       </c>
@@ -1619,9 +1613,6 @@
       <c r="O7" t="n">
         <v>13</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -1767,9 +1758,6 @@
       <c r="O8" t="n">
         <v>54</v>
       </c>
-      <c r="Q8" t="n">
-        <v>0</v>
-      </c>
       <c r="R8" t="n">
         <v>0.1046503758847705</v>
       </c>
@@ -1915,9 +1903,6 @@
       <c r="O9" t="n">
         <v>2</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0.01868976085656669</v>
       </c>
@@ -3051,9 +3036,6 @@
       <c r="O16" t="n">
         <v>13</v>
       </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
       <c r="R16" t="n">
         <v>0.1443193997023468</v>
       </c>
@@ -3361,9 +3343,6 @@
       <c r="O18" t="n">
         <v>3</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0.05336427512592412</v>
       </c>
@@ -3757,9 +3736,6 @@
       <c r="O20" t="n">
         <v>13</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0.1761851364255722</v>
       </c>
@@ -3905,9 +3881,6 @@
       <c r="O21" t="n">
         <v>35</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.06782894733272161</v>
       </c>
@@ -4053,9 +4026,6 @@
       <c r="O22" t="n">
         <v>4</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0.03737952171313338</v>
       </c>
@@ -5337,9 +5307,6 @@
       <c r="O30" t="n">
         <v>15</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.1665223842719386</v>
       </c>
@@ -5647,9 +5614,6 @@
       <c r="O32" t="n">
         <v>5</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0.08894045854320688</v>
       </c>
@@ -6043,9 +6007,6 @@
       <c r="O34" t="n">
         <v>14</v>
       </c>
-      <c r="Q34" t="n">
-        <v>0</v>
-      </c>
       <c r="R34" t="n">
         <v>0.1897378392275393</v>
       </c>
@@ -6191,9 +6152,6 @@
       <c r="O35" t="n">
         <v>68</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.1317819548178591</v>
       </c>
@@ -6339,9 +6297,6 @@
       <c r="O36" t="n">
         <v>6</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -7475,9 +7430,6 @@
       <c r="O43" t="n">
         <v>0</v>
       </c>
-      <c r="Q43" t="n">
-        <v>0</v>
-      </c>
       <c r="R43" t="n">
         <v>0</v>
       </c>
@@ -7623,9 +7575,6 @@
       <c r="O44" t="n">
         <v>9</v>
       </c>
-      <c r="Q44" t="n">
-        <v>0</v>
-      </c>
       <c r="R44" t="n">
         <v>0.09991343056316315</v>
       </c>
@@ -7933,9 +7882,6 @@
       <c r="O46" t="n">
         <v>6</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -8329,9 +8275,6 @@
       <c r="O48" t="n">
         <v>12</v>
       </c>
-      <c r="Q48" t="n">
-        <v>0</v>
-      </c>
       <c r="R48" t="n">
         <v>0.1626324336236051</v>
       </c>
@@ -8477,9 +8420,6 @@
       <c r="O49" t="n">
         <v>59</v>
       </c>
-      <c r="Q49" t="n">
-        <v>0</v>
-      </c>
       <c r="R49" t="n">
         <v>0.1143402255037307</v>
       </c>
@@ -8625,9 +8565,6 @@
       <c r="O50" t="n">
         <v>6</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -9021,9 +8958,6 @@
       <c r="O52" t="n">
         <v>1</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.004345692446436896</v>
       </c>
@@ -9761,9 +9695,6 @@
       <c r="O57" t="n">
         <v>0</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0</v>
       </c>
@@ -9909,9 +9840,6 @@
       <c r="O58" t="n">
         <v>7</v>
       </c>
-      <c r="Q58" t="n">
-        <v>0</v>
-      </c>
       <c r="R58" t="n">
         <v>0.07771044599357135</v>
       </c>
@@ -10219,9 +10147,6 @@
       <c r="O60" t="n">
         <v>6</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.1067285502518482</v>
       </c>
@@ -10615,9 +10540,6 @@
       <c r="O62" t="n">
         <v>15</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.2032905420295064</v>
       </c>
@@ -10763,9 +10685,6 @@
       <c r="O63" t="n">
         <v>79</v>
       </c>
-      <c r="Q63" t="n">
-        <v>0</v>
-      </c>
       <c r="R63" t="n">
         <v>0.1530996239795716</v>
       </c>
@@ -10911,9 +10830,6 @@
       <c r="O64" t="n">
         <v>6</v>
       </c>
-      <c r="Q64" t="n">
-        <v>0</v>
-      </c>
       <c r="R64" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -12047,9 +11963,6 @@
       <c r="O71" t="n">
         <v>0</v>
       </c>
-      <c r="Q71" t="n">
-        <v>0</v>
-      </c>
       <c r="R71" t="n">
         <v>0</v>
       </c>
@@ -12195,9 +12108,6 @@
       <c r="O72" t="n">
         <v>12</v>
       </c>
-      <c r="Q72" t="n">
-        <v>0</v>
-      </c>
       <c r="R72" t="n">
         <v>0.1332179074175509</v>
       </c>
@@ -12505,9 +12415,6 @@
       <c r="O74" t="n">
         <v>7</v>
       </c>
-      <c r="Q74" t="n">
-        <v>0</v>
-      </c>
       <c r="R74" t="n">
         <v>0.1245166419604896</v>
       </c>
@@ -12901,9 +12808,6 @@
       <c r="O76" t="n">
         <v>21</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0.284606758841309</v>
       </c>
@@ -13049,9 +12953,6 @@
       <c r="O77" t="n">
         <v>76</v>
       </c>
-      <c r="Q77" t="n">
-        <v>0</v>
-      </c>
       <c r="R77" t="n">
         <v>0.1472857142081955</v>
       </c>
@@ -13197,9 +13098,6 @@
       <c r="O78" t="n">
         <v>7</v>
       </c>
-      <c r="Q78" t="n">
-        <v>0</v>
-      </c>
       <c r="R78" t="n">
         <v>0.06541416299798342</v>
       </c>
@@ -13593,9 +13491,6 @@
       <c r="O80" t="n">
         <v>18</v>
       </c>
-      <c r="Q80" t="n">
-        <v>0</v>
-      </c>
       <c r="R80" t="n">
         <v>0.01470255133618379</v>
       </c>
@@ -13741,9 +13636,6 @@
       <c r="O81" t="n">
         <v>16</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -13889,9 +13781,6 @@
       <c r="O82" t="n">
         <v>16</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0.01306893452105226</v>
       </c>
@@ -14037,9 +13926,6 @@
       <c r="O83" t="n">
         <v>11</v>
       </c>
-      <c r="Q83" t="n">
-        <v>0</v>
-      </c>
       <c r="R83" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -14185,9 +14071,6 @@
       <c r="O84" t="n">
         <v>0</v>
       </c>
-      <c r="Q84" t="n">
-        <v>0</v>
-      </c>
       <c r="R84" t="n">
         <v>0</v>
       </c>
@@ -14328,16 +14211,13 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O85" t="n">
-        <v>11</v>
-      </c>
-      <c r="Q85" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R85" t="n">
-        <v>0.1956690087950551</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
@@ -14490,10 +14370,10 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O86" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="U86" t="inlineStr">
         <is>
@@ -14729,9 +14609,6 @@
       <c r="O87" t="n">
         <v>93</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0.1802312029126603</v>
       </c>
@@ -14877,9 +14754,6 @@
       <c r="O88" t="n">
         <v>6</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0.05606928256970008</v>
       </c>
@@ -15273,9 +15147,6 @@
       <c r="O90" t="n">
         <v>4</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0.01738276978574758</v>
       </c>
@@ -15421,9 +15292,6 @@
       <c r="O91" t="n">
         <v>8</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -15569,9 +15437,6 @@
       <c r="O92" t="n">
         <v>14</v>
       </c>
-      <c r="Q92" t="n">
-        <v>0</v>
-      </c>
       <c r="R92" t="n">
         <v>0.01143531770592073</v>
       </c>
@@ -15717,9 +15582,6 @@
       <c r="O93" t="n">
         <v>12</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0.009801700890789196</v>
       </c>
@@ -15865,9 +15727,6 @@
       <c r="O94" t="n">
         <v>11</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.00898489248322343</v>
       </c>
@@ -16013,9 +15872,6 @@
       <c r="O95" t="n">
         <v>8</v>
       </c>
-      <c r="Q95" t="n">
-        <v>0</v>
-      </c>
       <c r="R95" t="n">
         <v>0.00653446726052613</v>
       </c>
@@ -16161,9 +16017,6 @@
       <c r="O96" t="n">
         <v>0</v>
       </c>
-      <c r="Q96" t="n">
-        <v>0</v>
-      </c>
       <c r="R96" t="n">
         <v>0</v>
       </c>
@@ -16304,16 +16157,13 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O97" t="n">
-        <v>2</v>
-      </c>
-      <c r="Q97" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R97" t="n">
-        <v>0.03557618341728275</v>
+        <v>0.05336427512592412</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -16466,10 +16316,10 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="O98" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="U98" t="inlineStr">
         <is>
@@ -16700,16 +16550,13 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="O99" t="n">
-        <v>9</v>
-      </c>
-      <c r="Q99" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="R99" t="n">
-        <v>0.01744172931412841</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S99" t="inlineStr">
         <is>
@@ -16852,9 +16699,6 @@
       </c>
       <c r="O100" t="n">
         <v>13</v>
-      </c>
-      <c r="Q100" t="n">
-        <v>0</v>
       </c>
       <c r="R100" t="n">
         <v>0.01061850929835496</v>
@@ -17107,7 +16951,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18771</v>
+        <v>18776</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -14172,12 +14172,12 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CH</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Switzerland</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -14211,95 +14211,81 @@
         </is>
       </c>
       <c r="N85" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="O85" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="R85" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.06660895370877544</v>
       </c>
       <c r="S85" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA85" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO85" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP85" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ85" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS85" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR85" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS85" t="inlineStr"/>
       <c r="AT85" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU85" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>foph_idd</t>
         </is>
       </c>
       <c r="BA85" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Switzerland FOPH IDD</t>
         </is>
       </c>
       <c r="BB85" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.idd.bag.admin.ch/en/portal-data</t>
         </is>
       </c>
       <c r="BC85" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>rest_api</t>
         </is>
       </c>
     </row>
@@ -14326,7 +14312,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -14375,98 +14361,23 @@
       <c r="O86" t="n">
         <v>12</v>
       </c>
+      <c r="R86" t="n">
+        <v>0.2134571005036965</v>
+      </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U86" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V86" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W86" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X86" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y86" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD86" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE86" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF86" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG86" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH86" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI86" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ86" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK86" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM86" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN86" t="b">
-        <v>1</v>
       </c>
       <c r="AO86" t="inlineStr">
         <is>
@@ -14560,17 +14471,17 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -14604,81 +14515,170 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="O87" t="n">
-        <v>93</v>
-      </c>
-      <c r="R87" t="n">
-        <v>0.1802312029126603</v>
-      </c>
-      <c r="S87" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X87" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD87" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE87" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF87" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG87" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH87" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI87" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ87" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK87" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM87" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN87" t="b">
+        <v>1</v>
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR87" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS87" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ87" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS87" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14710,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14749,95 +14749,81 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="O88" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="R88" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U88" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AA88" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ88" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR88" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr"/>
       <c r="AT88" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -14864,7 +14850,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -14913,98 +14899,23 @@
       <c r="O89" t="n">
         <v>6</v>
       </c>
+      <c r="R89" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U89" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
-      <c r="V89" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W89" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X89" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y89" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD89" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE89" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF89" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG89" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH89" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI89" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ89" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK89" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM89" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN89" t="b">
-        <v>1</v>
       </c>
       <c r="AO89" t="inlineStr">
         <is>
@@ -15098,17 +15009,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -15142,81 +15053,170 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O90" t="n">
-        <v>4</v>
-      </c>
-      <c r="R90" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S90" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X90" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD90" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE90" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF90" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG90" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH90" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI90" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM90" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN90" t="b">
+        <v>1</v>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR90" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ90" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15248,12 +15248,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15278,7 +15278,7 @@
       </c>
       <c r="L91" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M91" t="inlineStr">
@@ -15287,13 +15287,13 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O91" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R91" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
@@ -15326,42 +15326,42 @@
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15423,7 +15423,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -15432,13 +15432,13 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="O92" t="n">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="R92" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S92" t="inlineStr">
         <is>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -15577,13 +15577,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O93" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R93" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -15713,7 +15713,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -15722,13 +15722,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="O94" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="R94" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -15858,7 +15858,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -15867,13 +15867,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O95" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R95" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -15973,12 +15973,12 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -16003,22 +16003,22 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O96" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16051,42 +16051,42 @@
       </c>
       <c r="AV96" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA96" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB96" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC96" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16118,12 +16118,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16157,95 +16157,81 @@
         </is>
       </c>
       <c r="N97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="O97" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>0.05336427512592412</v>
+        <v>0</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA97" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO97" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP97" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ97" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS97" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR97" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS97" t="inlineStr"/>
       <c r="AT97" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU97" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16258,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -16321,98 +16307,23 @@
       <c r="O98" t="n">
         <v>3</v>
       </c>
+      <c r="R98" t="n">
+        <v>0.05336427512592412</v>
+      </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U98" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W98" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X98" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y98" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD98" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE98" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF98" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG98" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH98" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI98" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM98" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN98" t="b">
-        <v>1</v>
       </c>
       <c r="AO98" t="inlineStr">
         <is>
@@ -16506,17 +16417,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16550,81 +16461,170 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O99" t="n">
-        <v>12</v>
-      </c>
-      <c r="R99" t="n">
-        <v>0.02325563908550455</v>
-      </c>
-      <c r="S99" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X99" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD99" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE99" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF99" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG99" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH99" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM99" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN99" t="b">
+        <v>1</v>
       </c>
       <c r="AO99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP99" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR99" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ99" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16656,12 +16656,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16686,7 +16686,7 @@
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -16695,13 +16695,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="O100" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="R100" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.02325563908550455</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16734,40 +16734,185 @@
       </c>
       <c r="AV100" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA100" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB100" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC100" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J101" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K101" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L101" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N101" t="n">
+        <v>13</v>
+      </c>
+      <c r="O101" t="n">
+        <v>13</v>
+      </c>
+      <c r="R101" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S101" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP101" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR101" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr"/>
+      <c r="AT101" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU101" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV101" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW100" t="inlineStr">
+      <c r="AW101" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX100" t="inlineStr">
+      <c r="AX101" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY100" t="inlineStr">
+      <c r="AY101" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ100" t="inlineStr">
+      <c r="AZ101" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA100" t="inlineStr">
+      <c r="BA101" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB100" t="inlineStr">
+      <c r="BB101" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC100" t="inlineStr">
+      <c r="BC101" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16889,7 +17034,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="10">
@@ -16899,7 +17044,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -16951,7 +17096,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18776</v>
+        <v>18782</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -16695,13 +16695,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="O100" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="R100" t="n">
-        <v>0.02325563908550455</v>
+        <v>0.02713157893308864</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -17096,7 +17096,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18782</v>
+        <v>18784</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -16302,13 +16302,13 @@
         </is>
       </c>
       <c r="N98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O98" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="R98" t="n">
-        <v>0.05336427512592412</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
@@ -16461,10 +16461,10 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="O99" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="U99" t="inlineStr">
         <is>
@@ -16695,13 +16695,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="O100" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="R100" t="n">
-        <v>0.02713157893308864</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16913,6 +16913,151 @@
         </is>
       </c>
       <c r="BC101" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K102" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L102" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N102" t="n">
+        <v>9</v>
+      </c>
+      <c r="O102" t="n">
+        <v>9</v>
+      </c>
+      <c r="R102" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S102" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP102" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR102" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS102" t="inlineStr"/>
+      <c r="AT102" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU102" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -16951,7 +17096,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-09</t>
         </is>
       </c>
     </row>
@@ -17034,7 +17179,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="10">
@@ -17044,7 +17189,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11">
@@ -17096,7 +17241,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18784</v>
+        <v>18796</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -14317,12 +14317,12 @@
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -14356,13 +14356,16 @@
         </is>
       </c>
       <c r="N86" t="n">
-        <v>12</v>
+        <v>2836</v>
       </c>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>2836</v>
+      </c>
+      <c r="Q86" t="n">
+        <v>1</v>
       </c>
       <c r="R86" t="n">
-        <v>0.2134571005036965</v>
+        <v>0.2007199180107829</v>
       </c>
       <c r="S86" t="inlineStr">
         <is>
@@ -14371,7 +14374,7 @@
       </c>
       <c r="U86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -14381,7 +14384,7 @@
       </c>
       <c r="AO86" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP86" t="inlineStr">
@@ -14391,12 +14394,12 @@
       </c>
       <c r="AQ86" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS86" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT86" t="n">
@@ -14404,47 +14407,47 @@
       </c>
       <c r="AU86" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA86" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB86" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC86" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -14476,12 +14479,12 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>CN</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>China</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -14515,29 +14518,29 @@
         </is>
       </c>
       <c r="N87" t="n">
-        <v>12</v>
+        <v>2836</v>
       </c>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>2836</v>
       </c>
       <c r="U87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="V87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>SRC_FI_THL_TTR</t>
+          <t>SRC_CN_CDC</t>
         </is>
       </c>
       <c r="X87" t="inlineStr">
         <is>
-          <t>Hepatitis E</t>
+          <t>戊型肝炎</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -14547,7 +14550,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>national_notifiable_disease_registry</t>
+          <t>notification</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -14562,7 +14565,7 @@
       </c>
       <c r="AC87" t="inlineStr">
         <is>
-          <t>country:FI:national</t>
+          <t>country:CN:national</t>
         </is>
       </c>
       <c r="AD87" t="inlineStr">
@@ -14577,7 +14580,7 @@
       </c>
       <c r="AF87" t="inlineStr">
         <is>
-          <t>conditional</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="AG87" t="inlineStr">
@@ -14597,17 +14600,17 @@
       </c>
       <c r="AJ87" t="inlineStr">
         <is>
-          <t>FI_THL_TTR_reporting_group</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK87" t="inlineStr">
         <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+          <t>China CDC source-reported hepatitis E component.</t>
         </is>
       </c>
       <c r="AM87" t="inlineStr">
         <is>
-          <t>provisional; raw</t>
+          <t>raw</t>
         </is>
       </c>
       <c r="AN87" t="b">
@@ -14615,7 +14618,7 @@
       </c>
       <c r="AO87" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>mixed</t>
         </is>
       </c>
       <c r="AP87" t="inlineStr">
@@ -14625,12 +14628,12 @@
       </c>
       <c r="AQ87" t="inlineStr">
         <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
+          <t>legacy_gap_fill</t>
         </is>
       </c>
       <c r="AS87" t="inlineStr">
         <is>
-          <t>SER_FI_THL_TTR_1340</t>
+          <t>SER_CN_HEPATITIS_E</t>
         </is>
       </c>
       <c r="AT87" t="n">
@@ -14638,47 +14641,47 @@
       </c>
       <c r="AU87" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>The public curve is read directly from one registered source series. Registry facts replace matching periods; legacy-only periods are retained as explicit coverage gap fills.</t>
         </is>
       </c>
       <c r="AV87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly</t>
         </is>
       </c>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>cdc_weekly; nhc; pubmed</t>
         </is>
       </c>
       <c r="BA87" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>China CDC Weekly; National Disease Control and Prevention Administration; PubMed</t>
         </is>
       </c>
       <c r="BB87" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://weekly.chinacdc.cn; https://www.ndcpa.gov.cn; https://pubmed.ncbi.nlm.nih.gov</t>
         </is>
       </c>
       <c r="BC87" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web; web; web</t>
         </is>
       </c>
     </row>
@@ -14710,12 +14713,12 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
@@ -14749,81 +14752,95 @@
         </is>
       </c>
       <c r="N88" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="O88" t="n">
-        <v>93</v>
+        <v>12</v>
       </c>
       <c r="R88" t="n">
-        <v>0.1802312029126603</v>
+        <v>0.2134571005036965</v>
       </c>
       <c r="S88" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP88" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR88" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS88" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ88" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS88" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU88" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA88" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB88" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC88" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -14850,17 +14867,17 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -14894,22 +14911,39 @@
         </is>
       </c>
       <c r="N89" t="n">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="O89" t="n">
-        <v>6</v>
-      </c>
-      <c r="R89" t="n">
-        <v>0.05606928256970008</v>
-      </c>
-      <c r="S89" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>12</v>
       </c>
       <c r="U89" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X89" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -14917,6 +14951,64 @@
           <t>monthly</t>
         </is>
       </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD89" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE89" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF89" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG89" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH89" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI89" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ89" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK89" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM89" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN89" t="b">
+        <v>1</v>
+      </c>
       <c r="AO89" t="inlineStr">
         <is>
           <t>series_registry</t>
@@ -14929,12 +15021,12 @@
       </c>
       <c r="AQ89" t="inlineStr">
         <is>
-          <t>parity</t>
+          <t>legacy_gap_fill_blocked_incompatible</t>
         </is>
       </c>
       <c r="AS89" t="inlineStr">
         <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+          <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
       <c r="AT89" t="n">
@@ -14942,47 +15034,47 @@
       </c>
       <c r="AU89" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA89" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB89" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC89" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -15009,17 +15101,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -15053,170 +15145,81 @@
         </is>
       </c>
       <c r="N90" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="O90" t="n">
-        <v>6</v>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X90" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD90" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE90" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF90" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG90" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH90" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI90" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ90" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK90" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM90" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN90" t="b">
-        <v>1</v>
+        <v>93</v>
+      </c>
+      <c r="R90" t="n">
+        <v>0.1802312029126603</v>
+      </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
       </c>
       <c r="AO90" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP90" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ90" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS90" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR90" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS90" t="inlineStr"/>
       <c r="AT90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU90" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA90" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB90" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC90" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -15248,12 +15251,12 @@
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -15287,81 +15290,95 @@
         </is>
       </c>
       <c r="N91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O91" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R91" t="n">
-        <v>0.01738276978574758</v>
+        <v>0.05606928256970008</v>
       </c>
       <c r="S91" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP91" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR91" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS91" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ91" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS91" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT91" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU91" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV91" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA91" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB91" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC91" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15388,17 +15405,17 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -15423,7 +15440,7 @@
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M92" t="inlineStr">
@@ -15432,81 +15449,170 @@
         </is>
       </c>
       <c r="N92" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O92" t="n">
-        <v>8</v>
-      </c>
-      <c r="R92" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S92" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X92" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD92" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE92" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF92" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG92" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH92" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI92" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ92" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK92" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM92" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN92" t="b">
+        <v>1</v>
       </c>
       <c r="AO92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP92" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS92" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ92" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS92" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU92" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA92" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB92" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC92" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -15538,12 +15644,12 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -15568,7 +15674,7 @@
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M93" t="inlineStr">
@@ -15577,13 +15683,13 @@
         </is>
       </c>
       <c r="N93" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O93" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="R93" t="n">
-        <v>0.01143531770592073</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S93" t="inlineStr">
         <is>
@@ -15616,42 +15722,42 @@
       </c>
       <c r="AV93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA93" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB93" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC93" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -15713,7 +15819,7 @@
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M94" t="inlineStr">
@@ -15722,13 +15828,13 @@
         </is>
       </c>
       <c r="N94" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="O94" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="R94" t="n">
-        <v>0.009801700890789196</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S94" t="inlineStr">
         <is>
@@ -15858,7 +15964,7 @@
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M95" t="inlineStr">
@@ -15867,13 +15973,13 @@
         </is>
       </c>
       <c r="N95" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="O95" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="R95" t="n">
-        <v>0.00898489248322343</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S95" t="inlineStr">
         <is>
@@ -16003,7 +16109,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -16012,13 +16118,13 @@
         </is>
       </c>
       <c r="N96" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="O96" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="R96" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S96" t="inlineStr">
         <is>
@@ -16118,12 +16224,12 @@
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -16148,22 +16254,22 @@
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="O97" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S97" t="inlineStr">
         <is>
@@ -16196,42 +16302,42 @@
       </c>
       <c r="AV97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA97" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB97" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC97" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16263,12 +16369,12 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -16293,104 +16399,90 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="O98" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="R98" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S98" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA98" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO98" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP98" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ98" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS98" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR98" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS98" t="inlineStr"/>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA98" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB98" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC98" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -16417,17 +16509,17 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -16461,170 +16553,81 @@
         </is>
       </c>
       <c r="N99" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="O99" t="n">
-        <v>4</v>
-      </c>
-      <c r="U99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="V99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W99" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X99" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y99" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
-      <c r="AA99" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD99" t="inlineStr">
+        <v>0</v>
+      </c>
+      <c r="R99" t="n">
+        <v>0</v>
+      </c>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP99" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR99" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS99" t="inlineStr"/>
+      <c r="AT99" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU99" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV99" t="inlineStr">
         <is>
           <t>all</t>
         </is>
       </c>
-      <c r="AE99" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF99" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG99" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH99" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI99" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ99" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK99" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM99" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN99" t="b">
-        <v>1</v>
-      </c>
-      <c r="AO99" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP99" t="inlineStr">
-        <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ99" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS99" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AT99" t="n">
-        <v>1</v>
-      </c>
-      <c r="AU99" t="inlineStr">
-        <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
-        </is>
-      </c>
-      <c r="AV99" t="inlineStr">
-        <is>
-          <t>thl_ttr</t>
-        </is>
-      </c>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA99" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB99" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC99" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -16656,12 +16659,12 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
@@ -16695,81 +16698,95 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="O100" t="n">
-        <v>16</v>
+        <v>4</v>
       </c>
       <c r="R100" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.07115236683456549</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP100" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR100" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS100" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ100" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS100" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU100" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA100" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB100" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC100" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16796,17 +16813,17 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -16831,7 +16848,7 @@
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -16840,81 +16857,170 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="O101" t="n">
-        <v>13</v>
-      </c>
-      <c r="R101" t="n">
-        <v>0.01061850929835496</v>
-      </c>
-      <c r="S101" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>4</v>
+      </c>
+      <c r="U101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W101" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X101" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y101" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA101" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD101" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE101" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF101" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG101" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH101" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ101" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK101" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM101" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN101" t="b">
+        <v>1</v>
       </c>
       <c r="AO101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP101" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR101" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS101" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ101" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS101" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV101" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA101" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB101" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC101" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -16946,12 +17052,12 @@
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
@@ -16976,7 +17082,7 @@
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M102" t="inlineStr">
@@ -16985,13 +17091,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="O102" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="R102" t="n">
-        <v>0.007351275668091897</v>
+        <v>0.03100751878067274</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -17024,40 +17130,330 @@
       </c>
       <c r="AV102" t="inlineStr">
         <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="AW102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="AX102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="AY102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>kdca_open_api</t>
+        </is>
+      </c>
+      <c r="BA102" t="inlineStr">
+        <is>
+          <t>Korea KDCA EID</t>
+        </is>
+      </c>
+      <c r="BB102" t="inlineStr">
+        <is>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+        </is>
+      </c>
+      <c r="BC102" t="inlineStr">
+        <is>
+          <t>open_api_or_portal_download</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J103" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K103" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L103" t="inlineStr">
+        <is>
+          <t>2026-08-02</t>
+        </is>
+      </c>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N103" t="n">
+        <v>13</v>
+      </c>
+      <c r="O103" t="n">
+        <v>13</v>
+      </c>
+      <c r="R103" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP103" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR103" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS103" t="inlineStr"/>
+      <c r="AT103" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU103" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV103" t="inlineStr">
+        <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="AW102" t="inlineStr">
+      <c r="AW103" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="AX102" t="inlineStr">
+      <c r="AX103" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="AY102" t="inlineStr">
+      <c r="AY103" t="inlineStr">
         <is>
           <t>web</t>
         </is>
       </c>
-      <c r="AZ102" t="inlineStr">
+      <c r="AZ103" t="inlineStr">
         <is>
           <t>jp_weekly</t>
         </is>
       </c>
-      <c r="BA102" t="inlineStr">
+      <c r="BA103" t="inlineStr">
         <is>
           <t>JP NIID Weekly</t>
         </is>
       </c>
-      <c r="BB102" t="inlineStr">
+      <c r="BB103" t="inlineStr">
         <is>
           <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
-      <c r="BC102" t="inlineStr">
+      <c r="BC103" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K104" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L104" t="inlineStr">
+        <is>
+          <t>2026-08-09</t>
+        </is>
+      </c>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N104" t="n">
+        <v>9</v>
+      </c>
+      <c r="O104" t="n">
+        <v>9</v>
+      </c>
+      <c r="R104" t="n">
+        <v>0.007351275668091897</v>
+      </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP104" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR104" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS104" t="inlineStr"/>
+      <c r="AT104" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU104" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA104" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB104" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC104" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17179,7 +17575,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="10">
@@ -17189,7 +17585,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>101</v>
+        <v>103</v>
       </c>
     </row>
     <row r="11">
@@ -17209,7 +17605,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="13">
@@ -17219,7 +17615,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
@@ -17241,7 +17637,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>18796</v>
+        <v>21632</v>
       </c>
     </row>
     <row r="16">
@@ -17251,7 +17647,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="17">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -12410,13 +12410,13 @@
         </is>
       </c>
       <c r="N74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O74" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R74" t="n">
-        <v>0.1245166419604896</v>
+        <v>0.1067285502518482</v>
       </c>
       <c r="S74" t="inlineStr">
         <is>
@@ -12569,10 +12569,10 @@
         </is>
       </c>
       <c r="N75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="O75" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U75" t="inlineStr">
         <is>
@@ -16698,13 +16698,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O100" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="R100" t="n">
-        <v>0.07115236683456549</v>
+        <v>0.08894045854320688</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="O101" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -16698,13 +16698,13 @@
         </is>
       </c>
       <c r="N100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O100" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="R100" t="n">
-        <v>0.08894045854320688</v>
+        <v>0.1245166419604896</v>
       </c>
       <c r="S100" t="inlineStr">
         <is>
@@ -16857,10 +16857,10 @@
         </is>
       </c>
       <c r="N101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="O101" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U101" t="inlineStr">
         <is>
@@ -17091,13 +17091,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="O102" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="R102" t="n">
-        <v>0.03100751878067274</v>
+        <v>0.0465112781710091</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>
@@ -17454,6 +17454,151 @@
         </is>
       </c>
       <c r="BC104" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>public_projection</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K105" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L105" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N105" t="n">
+        <v>8</v>
+      </c>
+      <c r="O105" t="n">
+        <v>8</v>
+      </c>
+      <c r="R105" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP105" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR105" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS105" t="inlineStr"/>
+      <c r="AT105" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU105" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
+      </c>
+      <c r="AV105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="AW105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="AX105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="AY105" t="inlineStr">
+        <is>
+          <t>web</t>
+        </is>
+      </c>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>jp_weekly</t>
+        </is>
+      </c>
+      <c r="BA105" t="inlineStr">
+        <is>
+          <t>JP NIID Weekly</t>
+        </is>
+      </c>
+      <c r="BB105" t="inlineStr">
+        <is>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+        </is>
+      </c>
+      <c r="BC105" t="inlineStr">
         <is>
           <t>web</t>
         </is>
@@ -17492,7 +17637,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-16</t>
         </is>
       </c>
     </row>
@@ -17575,7 +17720,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
     <row r="10">
@@ -17585,7 +17730,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
     </row>
     <row r="11">
@@ -17637,7 +17782,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21632</v>
+        <v>21650</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -12948,13 +12948,13 @@
         </is>
       </c>
       <c r="N77" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="O77" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="R77" t="n">
-        <v>0.1472857142081955</v>
+        <v>0.1453477442844034</v>
       </c>
       <c r="S77" t="inlineStr">
         <is>
@@ -17091,13 +17091,13 @@
         </is>
       </c>
       <c r="N102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="O102" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="R102" t="n">
-        <v>0.0465112781710091</v>
+        <v>0.04844924809480115</v>
       </c>
       <c r="S102" t="inlineStr">
         <is>

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -24844,7 +24844,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -24844,7 +24844,7 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -25350,12 +25350,12 @@
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>HK</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Hong Kong, China</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
@@ -25389,13 +25389,13 @@
         </is>
       </c>
       <c r="N142" t="n">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="O142" t="n">
-        <v>93</v>
+        <v>17</v>
       </c>
       <c r="R142" t="n">
-        <v>0.1802312029126603</v>
+        <v>0.2303959476334406</v>
       </c>
       <c r="S142" t="inlineStr">
         <is>
@@ -25428,42 +25428,42 @@
       </c>
       <c r="AV142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>chp_notifiable</t>
         </is>
       </c>
       <c r="BA142" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Hong Kong, China CHP Notifiable Diseases</t>
         </is>
       </c>
       <c r="BB142" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://www.chp.gov.hk/en/static/24012.html</t>
         </is>
       </c>
       <c r="BC142" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -25495,12 +25495,12 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>SE</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
@@ -25534,95 +25534,81 @@
         </is>
       </c>
       <c r="N143" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="O143" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="R143" t="n">
-        <v>0.05606928256970008</v>
+        <v>0.1802312029126603</v>
       </c>
       <c r="S143" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U143" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO143" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP143" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ143" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS143" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR143" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS143" t="inlineStr"/>
       <c r="AT143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU143" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>fohm_sminet</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA143" t="inlineStr">
         <is>
-          <t>Sweden Public Health Agency SmiNet</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB143" t="inlineStr">
         <is>
-          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC143" t="inlineStr">
         <is>
-          <t>official_html_csv</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -25649,7 +25635,7 @@
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
@@ -25698,98 +25684,23 @@
       <c r="O144" t="n">
         <v>6</v>
       </c>
+      <c r="R144" t="n">
+        <v>0.05606928256970008</v>
+      </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U144" t="inlineStr">
         <is>
           <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
         </is>
       </c>
-      <c r="V144" t="inlineStr">
-        <is>
-          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W144" t="inlineStr">
-        <is>
-          <t>SRC_SE_FOHM_SMINET</t>
-        </is>
-      </c>
-      <c r="X144" t="inlineStr">
-        <is>
-          <t>Hepatit E</t>
-        </is>
-      </c>
-      <c r="Y144" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA144" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>country:SE:national</t>
-        </is>
-      </c>
-      <c r="AD144" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE144" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF144" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG144" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH144" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ144" t="inlineStr">
-        <is>
-          <t>SE_FOHM_SMINET_current</t>
-        </is>
-      </c>
-      <c r="AK144" t="inlineStr">
-        <is>
-          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
-        </is>
-      </c>
-      <c r="AM144" t="inlineStr">
-        <is>
-          <t>revised</t>
-        </is>
-      </c>
-      <c r="AN144" t="b">
-        <v>1</v>
       </c>
       <c r="AO144" t="inlineStr">
         <is>
@@ -25883,17 +25794,17 @@
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>TW</t>
+          <t>SE</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Taiwan, China</t>
+          <t>Sweden</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -25927,81 +25838,170 @@
         </is>
       </c>
       <c r="N145" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="O145" t="n">
-        <v>4</v>
-      </c>
-      <c r="R145" t="n">
-        <v>0.01738276978574758</v>
-      </c>
-      <c r="S145" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="U145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W145" t="inlineStr">
+        <is>
+          <t>SRC_SE_FOHM_SMINET</t>
+        </is>
+      </c>
+      <c r="X145" t="inlineStr">
+        <is>
+          <t>Hepatit E</t>
+        </is>
+      </c>
+      <c r="Y145" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z145" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA145" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB145" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>country:SE:national</t>
+        </is>
+      </c>
+      <c r="AD145" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE145" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF145" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG145" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH145" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ145" t="inlineStr">
+        <is>
+          <t>SE_FOHM_SMINET_current</t>
+        </is>
+      </c>
+      <c r="AK145" t="inlineStr">
+        <is>
+          <t>Sweden FHM SmiNet national monthly notification series; FHM SmiNet monthly national total.</t>
+        </is>
+      </c>
+      <c r="AM145" t="inlineStr">
+        <is>
+          <t>revised</t>
+        </is>
+      </c>
+      <c r="AN145" t="b">
+        <v>1</v>
       </c>
       <c r="AO145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP145" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR145" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS145" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ145" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS145" t="inlineStr">
+        <is>
+          <t>SER_SE_FOHM_SMINET_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT145" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU145" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series.</t>
         </is>
       </c>
       <c r="AV145" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>nidss_open_data</t>
+          <t>fohm_sminet</t>
         </is>
       </c>
       <c r="BA145" t="inlineStr">
         <is>
-          <t>Taiwan, China CDC NIDSS</t>
+          <t>Sweden Public Health Agency SmiNet</t>
         </is>
       </c>
       <c r="BB145" t="inlineStr">
         <is>
-          <t>https://nidss.cdc.gov.tw/Home/Index</t>
+          <t>https://www.folkhalsomyndigheten.se/statistik-och-data/hitta-statistik-och-data/smittsamma-sjukdomar-statistik/</t>
         </is>
       </c>
       <c r="BC145" t="inlineStr">
         <is>
-          <t>open_data_csv</t>
+          <t>official_html_csv</t>
         </is>
       </c>
     </row>
@@ -26033,12 +26033,12 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>TW</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Taiwan, China</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -26063,7 +26063,7 @@
       </c>
       <c r="L146" t="inlineStr">
         <is>
-          <t>2026-07-04</t>
+          <t>2026-07-01</t>
         </is>
       </c>
       <c r="M146" t="inlineStr">
@@ -26072,13 +26072,13 @@
         </is>
       </c>
       <c r="N146" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="O146" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="R146" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.01738276978574758</v>
       </c>
       <c r="S146" t="inlineStr">
         <is>
@@ -26111,42 +26111,42 @@
       </c>
       <c r="AV146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>nidss_open_data</t>
         </is>
       </c>
       <c r="BA146" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Taiwan, China CDC NIDSS</t>
         </is>
       </c>
       <c r="BB146" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://nidss.cdc.gov.tw/Home/Index</t>
         </is>
       </c>
       <c r="BC146" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_data_csv</t>
         </is>
       </c>
     </row>
@@ -26178,12 +26178,12 @@
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -26208,7 +26208,7 @@
       </c>
       <c r="L147" t="inlineStr">
         <is>
-          <t>2026-07-05</t>
+          <t>2026-07-04</t>
         </is>
       </c>
       <c r="M147" t="inlineStr">
@@ -26217,93 +26217,81 @@
         </is>
       </c>
       <c r="N147" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="O147" t="n">
-        <v>1</v>
-      </c>
-      <c r="P147" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="R147" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S147" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA147" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO147" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP147" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ147" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS147" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR147" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS147" t="inlineStr"/>
       <c r="AT147" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU147" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA147" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB147" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC147" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26330,7 +26318,7 @@
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
@@ -26382,98 +26370,18 @@
       <c r="P148" t="n">
         <v>1</v>
       </c>
-      <c r="U148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V148" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W148" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X148" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y148" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z148" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R148" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S148" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB148" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD148" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE148" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF148" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG148" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH148" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI148" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ148" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK148" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM148" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN148" t="b">
-        <v>1</v>
       </c>
       <c r="AO148" t="inlineStr">
         <is>
@@ -26567,17 +26475,17 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
@@ -26602,7 +26510,7 @@
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>2026-07-11</t>
+          <t>2026-07-05</t>
         </is>
       </c>
       <c r="M149" t="inlineStr">
@@ -26611,81 +26519,173 @@
         </is>
       </c>
       <c r="N149" t="n">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="O149" t="n">
-        <v>14</v>
-      </c>
-      <c r="R149" t="n">
-        <v>0.01143531770592073</v>
-      </c>
-      <c r="S149" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P149" t="n">
+        <v>1</v>
+      </c>
+      <c r="U149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W149" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X149" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y149" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z149" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA149" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB149" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC149" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD149" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE149" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF149" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG149" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH149" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI149" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ149" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK149" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM149" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN149" t="b">
+        <v>1</v>
       </c>
       <c r="AO149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP149" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR149" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS149" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ149" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS149" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT149" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU149" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA149" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB149" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC149" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -26717,12 +26717,12 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -26747,7 +26747,7 @@
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2026-07-11</t>
         </is>
       </c>
       <c r="M150" t="inlineStr">
@@ -26756,93 +26756,81 @@
         </is>
       </c>
       <c r="N150" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="O150" t="n">
-        <v>3</v>
-      </c>
-      <c r="P150" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="R150" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.01143531770592073</v>
       </c>
       <c r="S150" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA150" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO150" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP150" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ150" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS150" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR150" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS150" t="inlineStr"/>
       <c r="AT150" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU150" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA150" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB150" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC150" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -26869,7 +26857,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -26921,98 +26909,18 @@
       <c r="P151" t="n">
         <v>3</v>
       </c>
-      <c r="U151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V151" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W151" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X151" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y151" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z151" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R151" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S151" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB151" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD151" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE151" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF151" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG151" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH151" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ151" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK151" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM151" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN151" t="b">
-        <v>1</v>
       </c>
       <c r="AO151" t="inlineStr">
         <is>
@@ -27106,17 +27014,17 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -27141,7 +27049,7 @@
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>2026-07-18</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="M152" t="inlineStr">
@@ -27150,81 +27058,173 @@
         </is>
       </c>
       <c r="N152" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="O152" t="n">
-        <v>12</v>
-      </c>
-      <c r="R152" t="n">
-        <v>0.009801700890789196</v>
-      </c>
-      <c r="S152" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P152" t="n">
+        <v>3</v>
+      </c>
+      <c r="U152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W152" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X152" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y152" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA152" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC152" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD152" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE152" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF152" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG152" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH152" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI152" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM152" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN152" t="b">
+        <v>1</v>
       </c>
       <c r="AO152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP152" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR152" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS152" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ152" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS152" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT152" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU152" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA152" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB152" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC152" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27256,12 +27256,12 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -27286,7 +27286,7 @@
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>2026-07-19</t>
+          <t>2026-07-18</t>
         </is>
       </c>
       <c r="M153" t="inlineStr">
@@ -27295,93 +27295,81 @@
         </is>
       </c>
       <c r="N153" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="O153" t="n">
-        <v>1</v>
-      </c>
-      <c r="P153" t="n">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="R153" t="n">
-        <v>0.01693265755097047</v>
+        <v>0.009801700890789196</v>
       </c>
       <c r="S153" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA153" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO153" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP153" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ153" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS153" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR153" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS153" t="inlineStr"/>
       <c r="AT153" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU153" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA153" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB153" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC153" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -27408,7 +27396,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -27460,98 +27448,18 @@
       <c r="P154" t="n">
         <v>1</v>
       </c>
-      <c r="U154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V154" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W154" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X154" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y154" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z154" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R154" t="n">
+        <v>0.01693265755097047</v>
+      </c>
+      <c r="S154" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB154" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD154" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE154" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF154" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG154" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH154" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI154" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ154" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK154" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM154" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN154" t="b">
-        <v>1</v>
       </c>
       <c r="AO154" t="inlineStr">
         <is>
@@ -27645,17 +27553,17 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -27680,7 +27588,7 @@
       </c>
       <c r="L155" t="inlineStr">
         <is>
-          <t>2026-07-25</t>
+          <t>2026-07-19</t>
         </is>
       </c>
       <c r="M155" t="inlineStr">
@@ -27689,81 +27597,173 @@
         </is>
       </c>
       <c r="N155" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="O155" t="n">
-        <v>11</v>
-      </c>
-      <c r="R155" t="n">
-        <v>0.00898489248322343</v>
-      </c>
-      <c r="S155" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>1</v>
+      </c>
+      <c r="P155" t="n">
+        <v>1</v>
+      </c>
+      <c r="U155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W155" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X155" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y155" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z155" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA155" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB155" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD155" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE155" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF155" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG155" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH155" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI155" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ155" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK155" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM155" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN155" t="b">
+        <v>1</v>
       </c>
       <c r="AO155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP155" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR155" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS155" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ155" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS155" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT155" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU155" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA155" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB155" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC155" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -27825,7 +27825,7 @@
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>2026-07-26</t>
+          <t>2026-07-25</t>
         </is>
       </c>
       <c r="M156" t="inlineStr">
@@ -27834,13 +27834,13 @@
         </is>
       </c>
       <c r="N156" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="O156" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="R156" t="n">
-        <v>0.00653446726052613</v>
+        <v>0.00898489248322343</v>
       </c>
       <c r="S156" t="inlineStr">
         <is>
@@ -27940,12 +27940,12 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
@@ -27979,93 +27979,81 @@
         </is>
       </c>
       <c r="N157" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="O157" t="n">
-        <v>2</v>
-      </c>
-      <c r="P157" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="R157" t="n">
-        <v>0.03386531510194095</v>
+        <v>0.00653446726052613</v>
       </c>
       <c r="S157" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA157" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO157" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP157" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ157" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS157" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR157" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS157" t="inlineStr"/>
       <c r="AT157" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU157" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV157" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA157" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB157" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC157" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -28092,7 +28080,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -28144,98 +28132,18 @@
       <c r="P158" t="n">
         <v>2</v>
       </c>
-      <c r="U158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V158" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W158" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X158" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y158" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R158" t="n">
+        <v>0.03386531510194095</v>
+      </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD158" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE158" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF158" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG158" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH158" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI158" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ158" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK158" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM158" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN158" t="b">
-        <v>1</v>
       </c>
       <c r="AO158" t="inlineStr">
         <is>
@@ -28329,17 +28237,17 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>AU</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
@@ -28364,90 +28272,182 @@
       </c>
       <c r="L159" t="inlineStr">
         <is>
-          <t>2026-08-01</t>
+          <t>2026-07-26</t>
         </is>
       </c>
       <c r="M159" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="N159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O159" t="n">
-        <v>0</v>
-      </c>
-      <c r="R159" t="n">
-        <v>0</v>
-      </c>
-      <c r="S159" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>2</v>
+      </c>
+      <c r="P159" t="n">
+        <v>2</v>
+      </c>
+      <c r="U159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W159" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X159" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y159" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z159" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA159" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB159" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC159" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD159" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE159" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF159" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG159" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH159" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI159" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ159" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK159" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM159" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN159" t="b">
+        <v>1</v>
       </c>
       <c r="AO159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP159" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR159" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS159" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ159" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS159" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT159" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU159" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>all</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA159" t="inlineStr">
         <is>
-          <t>Australia NINDSS</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB159" t="inlineStr">
         <is>
-          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC159" t="inlineStr">
         <is>
-          <t>microsoft_bi</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -28479,12 +28479,12 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>FI</t>
+          <t>AU</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -28518,95 +28518,81 @@
         </is>
       </c>
       <c r="N160" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O160" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="R160" t="n">
-        <v>0.142304733669131</v>
+        <v>0</v>
       </c>
       <c r="S160" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="AA160" t="inlineStr">
-        <is>
-          <t>monthly</t>
-        </is>
-      </c>
       <c r="AO160" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP160" t="inlineStr">
         <is>
-          <t>single_series</t>
-        </is>
-      </c>
-      <c r="AQ160" t="inlineStr">
-        <is>
-          <t>legacy_gap_fill_blocked_incompatible</t>
-        </is>
-      </c>
-      <c r="AS160" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR160" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS160" t="inlineStr"/>
       <c r="AT160" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU160" t="inlineStr">
         <is>
-          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>thl_ttr</t>
+          <t>all</t>
         </is>
       </c>
       <c r="BA160" t="inlineStr">
         <is>
-          <t>Finland THL Infectious Diseases Register</t>
+          <t>Australia NINDSS</t>
         </is>
       </c>
       <c r="BB160" t="inlineStr">
         <is>
-          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
+          <t>https://www.health.gov.au/topics/national-notifiable-diseases-surveillance-system-nndss</t>
         </is>
       </c>
       <c r="BC160" t="inlineStr">
         <is>
-          <t>cube_csv</t>
+          <t>microsoft_bi</t>
         </is>
       </c>
     </row>
@@ -28633,7 +28619,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -28682,98 +28668,23 @@
       <c r="O161" t="n">
         <v>8</v>
       </c>
+      <c r="R161" t="n">
+        <v>0.142304733669131</v>
+      </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="U161" t="inlineStr">
         <is>
           <t>SER_FI_THL_TTR_1340</t>
         </is>
       </c>
-      <c r="V161" t="inlineStr">
-        <is>
-          <t>SER_FI_THL_TTR_1340</t>
-        </is>
-      </c>
-      <c r="W161" t="inlineStr">
-        <is>
-          <t>SRC_FI_THL_TTR</t>
-        </is>
-      </c>
-      <c r="X161" t="inlineStr">
-        <is>
-          <t>Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y161" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_registry</t>
-        </is>
-      </c>
       <c r="AA161" t="inlineStr">
         <is>
           <t>monthly</t>
         </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>country:FI:national</t>
-        </is>
-      </c>
-      <c r="AD161" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE161" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF161" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG161" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH161" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI161" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ161" t="inlineStr">
-        <is>
-          <t>FI_THL_TTR_reporting_group</t>
-        </is>
-      </c>
-      <c r="AK161" t="inlineStr">
-        <is>
-          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
-        </is>
-      </c>
-      <c r="AM161" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN161" t="b">
-        <v>1</v>
       </c>
       <c r="AO161" t="inlineStr">
         <is>
@@ -28867,17 +28778,17 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>KR</t>
+          <t>FI</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>South Korea</t>
+          <t>Finland</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
@@ -28911,81 +28822,170 @@
         </is>
       </c>
       <c r="N162" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="O162" t="n">
-        <v>25</v>
-      </c>
-      <c r="R162" t="n">
-        <v>0.04844924809480115</v>
-      </c>
-      <c r="S162" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="U162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="V162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
+      <c r="W162" t="inlineStr">
+        <is>
+          <t>SRC_FI_THL_TTR</t>
+        </is>
+      </c>
+      <c r="X162" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y162" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_registry</t>
+        </is>
+      </c>
+      <c r="AA162" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>country:FI:national</t>
+        </is>
+      </c>
+      <c r="AD162" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE162" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF162" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG162" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH162" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI162" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ162" t="inlineStr">
+        <is>
+          <t>FI_THL_TTR_reporting_group</t>
+        </is>
+      </c>
+      <c r="AK162" t="inlineStr">
+        <is>
+          <t>Finland THL national monthly notification series; THL reporting group code 1340.</t>
+        </is>
+      </c>
+      <c r="AM162" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN162" t="b">
+        <v>1</v>
       </c>
       <c r="AO162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP162" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR162" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS162" t="inlineStr"/>
+          <t>single_series</t>
+        </is>
+      </c>
+      <c r="AQ162" t="inlineStr">
+        <is>
+          <t>legacy_gap_fill_blocked_incompatible</t>
+        </is>
+      </c>
+      <c r="AS162" t="inlineStr">
+        <is>
+          <t>SER_FI_THL_TTR_1340</t>
+        </is>
+      </c>
       <c r="AT162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU162" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>The public curve is read directly from one registered source series. Legacy rows with a different reporting grain or comparison basis were not joined to this curve.</t>
         </is>
       </c>
       <c r="AV162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>kdca_open_api</t>
+          <t>thl_ttr</t>
         </is>
       </c>
       <c r="BA162" t="inlineStr">
         <is>
-          <t>Korea KDCA EID</t>
+          <t>Finland THL Infectious Diseases Register</t>
         </is>
       </c>
       <c r="BB162" t="inlineStr">
         <is>
-          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
+          <t>https://sampo.thl.fi/pivot/prod/en/ttr/cases/fact_ttr_cases</t>
         </is>
       </c>
       <c r="BC162" t="inlineStr">
         <is>
-          <t>open_api_or_portal_download</t>
+          <t>cube_csv</t>
         </is>
       </c>
     </row>
@@ -29017,12 +29017,12 @@
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>KR</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -29047,7 +29047,7 @@
       </c>
       <c r="L163" t="inlineStr">
         <is>
-          <t>2026-08-02</t>
+          <t>2026-08-01</t>
         </is>
       </c>
       <c r="M163" t="inlineStr">
@@ -29056,13 +29056,13 @@
         </is>
       </c>
       <c r="N163" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="O163" t="n">
-        <v>13</v>
+        <v>28</v>
       </c>
       <c r="R163" t="n">
-        <v>0.01061850929835496</v>
+        <v>0.05426315786617728</v>
       </c>
       <c r="S163" t="inlineStr">
         <is>
@@ -29095,42 +29095,42 @@
       </c>
       <c r="AV163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>kdca_open_api</t>
         </is>
       </c>
       <c r="BA163" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Korea KDCA EID</t>
         </is>
       </c>
       <c r="BB163" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.data.go.kr/data/15139178/openapi.do</t>
         </is>
       </c>
       <c r="BC163" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>open_api_or_portal_download</t>
         </is>
       </c>
     </row>
@@ -29162,12 +29162,12 @@
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -29201,93 +29201,81 @@
         </is>
       </c>
       <c r="N164" t="n">
+        <v>13</v>
+      </c>
+      <c r="O164" t="n">
+        <v>13</v>
+      </c>
+      <c r="R164" t="n">
+        <v>0.01061850929835496</v>
+      </c>
+      <c r="S164" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP164" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR164" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS164" t="inlineStr"/>
+      <c r="AT164" t="n">
         <v>0</v>
       </c>
-      <c r="O164" t="n">
-        <v>0</v>
-      </c>
-      <c r="P164" t="n">
-        <v>0</v>
-      </c>
-      <c r="R164" t="n">
-        <v>0</v>
-      </c>
-      <c r="S164" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA164" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP164" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ164" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS164" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT164" t="n">
-        <v>2</v>
-      </c>
       <c r="AU164" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA164" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB164" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC164" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29314,7 +29302,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -29366,98 +29354,18 @@
       <c r="P165" t="n">
         <v>0</v>
       </c>
-      <c r="U165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V165" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W165" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X165" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y165" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z165" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R165" t="n">
+        <v>0</v>
+      </c>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB165" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD165" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE165" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF165" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG165" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH165" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI165" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN165" t="b">
-        <v>1</v>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
@@ -29551,17 +29459,17 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -29586,7 +29494,7 @@
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>2026-08-09</t>
+          <t>2026-08-02</t>
         </is>
       </c>
       <c r="M166" t="inlineStr">
@@ -29595,81 +29503,173 @@
         </is>
       </c>
       <c r="N166" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="O166" t="n">
-        <v>9</v>
-      </c>
-      <c r="R166" t="n">
-        <v>0.007351275668091897</v>
-      </c>
-      <c r="S166" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>0</v>
+      </c>
+      <c r="P166" t="n">
+        <v>0</v>
+      </c>
+      <c r="U166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W166" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X166" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y166" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA166" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD166" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE166" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF166" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG166" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH166" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI166" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ166" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK166" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN166" t="b">
+        <v>1</v>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP166" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR166" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS166" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ166" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS166" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT166" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU166" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA166" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB166" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC166" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -29701,12 +29701,12 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -29740,93 +29740,81 @@
         </is>
       </c>
       <c r="N167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="O167" t="n">
-        <v>3</v>
-      </c>
-      <c r="P167" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="R167" t="n">
-        <v>0.05079797265291142</v>
+        <v>0.007351275668091897</v>
       </c>
       <c r="S167" t="inlineStr">
         <is>
           <t>wpp_computed</t>
         </is>
       </c>
-      <c r="AA167" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
       <c r="AO167" t="inlineStr">
         <is>
-          <t>series_registry</t>
+          <t>legacy_fallback</t>
         </is>
       </c>
       <c r="AP167" t="inlineStr">
         <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ167" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS167" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR167" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS167" t="inlineStr"/>
       <c r="AT167" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AU167" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA167" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB167" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC167" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -29853,7 +29841,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -29905,98 +29893,18 @@
       <c r="P168" t="n">
         <v>3</v>
       </c>
-      <c r="U168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V168" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W168" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X168" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y168" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z168" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R168" t="n">
+        <v>0.05079797265291142</v>
+      </c>
+      <c r="S168" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB168" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC168" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD168" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE168" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF168" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG168" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH168" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI168" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ168" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK168" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM168" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN168" t="b">
-        <v>1</v>
       </c>
       <c r="AO168" t="inlineStr">
         <is>
@@ -30090,17 +29998,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>public_projection</t>
+          <t>source_series_observation</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>JP</t>
+          <t>SG</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -30125,7 +30033,7 @@
       </c>
       <c r="L169" t="inlineStr">
         <is>
-          <t>2026-08-16</t>
+          <t>2026-08-09</t>
         </is>
       </c>
       <c r="M169" t="inlineStr">
@@ -30134,81 +30042,173 @@
         </is>
       </c>
       <c r="N169" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="O169" t="n">
-        <v>8</v>
-      </c>
-      <c r="R169" t="n">
-        <v>0.00653446726052613</v>
-      </c>
-      <c r="S169" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
+        <v>3</v>
+      </c>
+      <c r="P169" t="n">
+        <v>3</v>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X169" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC169" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD169" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE169" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF169" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG169" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH169" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI169" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ169" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK169" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM169" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN169" t="b">
+        <v>1</v>
       </c>
       <c r="AO169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
+          <t>series_registry</t>
         </is>
       </c>
       <c r="AP169" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR169" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
-        </is>
-      </c>
-      <c r="AS169" t="inlineStr"/>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ169" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS169" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
       <c r="AT169" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AU169" t="inlineStr">
         <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
         </is>
       </c>
       <c r="AV169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>jp_weekly</t>
+          <t>cda_weekly_bulletin</t>
         </is>
       </c>
       <c r="BA169" t="inlineStr">
         <is>
-          <t>JP NIID Weekly</t>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
         </is>
       </c>
       <c r="BB169" t="inlineStr">
         <is>
-          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
         </is>
       </c>
       <c r="BC169" t="inlineStr">
         <is>
-          <t>web</t>
+          <t>official_csv_and_workbook</t>
         </is>
       </c>
     </row>
@@ -30240,12 +30240,12 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>SG</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
@@ -30279,93 +30279,81 @@
         </is>
       </c>
       <c r="N170" t="n">
+        <v>8</v>
+      </c>
+      <c r="O170" t="n">
+        <v>8</v>
+      </c>
+      <c r="R170" t="n">
+        <v>0.00653446726052613</v>
+      </c>
+      <c r="S170" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AP170" t="inlineStr">
+        <is>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR170" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
+        </is>
+      </c>
+      <c r="AS170" t="inlineStr"/>
+      <c r="AT170" t="n">
         <v>0</v>
       </c>
-      <c r="O170" t="n">
-        <v>0</v>
-      </c>
-      <c r="P170" t="n">
-        <v>0</v>
-      </c>
-      <c r="R170" t="n">
-        <v>0</v>
-      </c>
-      <c r="S170" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
-      <c r="AA170" t="inlineStr">
-        <is>
-          <t>weekly</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>series_registry</t>
-        </is>
-      </c>
-      <c r="AP170" t="inlineStr">
-        <is>
-          <t>temporal_handoff</t>
-        </is>
-      </c>
-      <c r="AQ170" t="inlineStr">
-        <is>
-          <t>parity</t>
-        </is>
-      </c>
-      <c r="AS170" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="AT170" t="n">
-        <v>2</v>
-      </c>
       <c r="AU170" t="inlineStr">
         <is>
-          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
         </is>
       </c>
       <c r="AV170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="AW170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="AX170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="AY170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>cda_weekly_bulletin</t>
+          <t>jp_weekly</t>
         </is>
       </c>
       <c r="BA170" t="inlineStr">
         <is>
-          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+          <t>JP NIID Weekly</t>
         </is>
       </c>
       <c r="BB170" t="inlineStr">
         <is>
-          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+          <t>https://id-info.jihs.go.jp/en/surveillance/idwr/rapid/index.html</t>
         </is>
       </c>
       <c r="BC170" t="inlineStr">
         <is>
-          <t>official_csv_and_workbook</t>
+          <t>web</t>
         </is>
       </c>
     </row>
@@ -30392,7 +30380,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>source_series_observation</t>
+          <t>public_projection</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -30444,98 +30432,18 @@
       <c r="P171" t="n">
         <v>0</v>
       </c>
-      <c r="U171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="V171" t="inlineStr">
-        <is>
-          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
-        </is>
-      </c>
-      <c r="W171" t="inlineStr">
-        <is>
-          <t>SRC_SG_CDA_WIDB</t>
-        </is>
-      </c>
-      <c r="X171" t="inlineStr">
-        <is>
-          <t>Acute Viral Hepatitis E</t>
-        </is>
-      </c>
-      <c r="Y171" t="inlineStr">
-        <is>
-          <t>case_notifications</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>national_notifiable_disease_surveillance</t>
+      <c r="R171" t="n">
+        <v>0</v>
+      </c>
+      <c r="S171" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
           <t>weekly</t>
         </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>count</t>
-        </is>
-      </c>
-      <c r="AC171" t="inlineStr">
-        <is>
-          <t>country:SG:national</t>
-        </is>
-      </c>
-      <c r="AD171" t="inlineStr">
-        <is>
-          <t>all</t>
-        </is>
-      </c>
-      <c r="AE171" t="inlineStr">
-        <is>
-          <t>exact</t>
-        </is>
-      </c>
-      <c r="AF171" t="inlineStr">
-        <is>
-          <t>conditional</t>
-        </is>
-      </c>
-      <c r="AG171" t="inlineStr">
-        <is>
-          <t>non_additive</t>
-        </is>
-      </c>
-      <c r="AH171" t="inlineStr">
-        <is>
-          <t>active</t>
-        </is>
-      </c>
-      <c r="AI171" t="inlineStr">
-        <is>
-          <t>missing_is_unknown</t>
-        </is>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>SG_CDA_WIDB_2023_CURRENT</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
-        </is>
-      </c>
-      <c r="AM171" t="inlineStr">
-        <is>
-          <t>provisional; raw</t>
-        </is>
-      </c>
-      <c r="AN171" t="b">
-        <v>1</v>
       </c>
       <c r="AO171" t="inlineStr">
         <is>
@@ -30601,6 +30509,243 @@
         </is>
       </c>
       <c r="BC171" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>disease</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>hepatitis-e</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>source_series_observation</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>SG</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>D011</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>Hepatitis E</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr">
+        <is>
+          <t>戊型肝炎</t>
+        </is>
+      </c>
+      <c r="K172" t="inlineStr">
+        <is>
+          <t>Viral</t>
+        </is>
+      </c>
+      <c r="L172" t="inlineStr">
+        <is>
+          <t>2026-08-16</t>
+        </is>
+      </c>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="N172" t="n">
+        <v>0</v>
+      </c>
+      <c r="O172" t="n">
+        <v>0</v>
+      </c>
+      <c r="P172" t="n">
+        <v>0</v>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>SRC_SG_CDA_WIDB</t>
+        </is>
+      </c>
+      <c r="X172" t="inlineStr">
+        <is>
+          <t>Acute Viral Hepatitis E</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>case_notifications</t>
+        </is>
+      </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>national_notifiable_disease_surveillance</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>weekly</t>
+        </is>
+      </c>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>count</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>country:SG:national</t>
+        </is>
+      </c>
+      <c r="AD172" t="inlineStr">
+        <is>
+          <t>all</t>
+        </is>
+      </c>
+      <c r="AE172" t="inlineStr">
+        <is>
+          <t>exact</t>
+        </is>
+      </c>
+      <c r="AF172" t="inlineStr">
+        <is>
+          <t>conditional</t>
+        </is>
+      </c>
+      <c r="AG172" t="inlineStr">
+        <is>
+          <t>non_additive</t>
+        </is>
+      </c>
+      <c r="AH172" t="inlineStr">
+        <is>
+          <t>active</t>
+        </is>
+      </c>
+      <c r="AI172" t="inlineStr">
+        <is>
+          <t>missing_is_unknown</t>
+        </is>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>SG_CDA_WIDB_2023_CURRENT</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Singapore CDA weekly notification table from 2023+ annual workbooks with 2023 PDFs as failover; zero is explicit, future blanks are unknown, and public release is enabled by explicit operator authorization; CDA source terms still require written permission.</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>provisional; raw</t>
+        </is>
+      </c>
+      <c r="AN172" t="b">
+        <v>1</v>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>series_registry</t>
+        </is>
+      </c>
+      <c r="AP172" t="inlineStr">
+        <is>
+          <t>temporal_handoff</t>
+        </is>
+      </c>
+      <c r="AQ172" t="inlineStr">
+        <is>
+          <t>parity</t>
+        </is>
+      </c>
+      <c r="AS172" t="inlineStr">
+        <is>
+          <t>SER_SG_CDA_ACUTE_VIRAL_HEPATITIS_E; SER_SG_HIST_ACUTE_VIRAL_HEPATITIS_E</t>
+        </is>
+      </c>
+      <c r="AT172" t="n">
+        <v>2</v>
+      </c>
+      <c r="AU172" t="inlineStr">
+        <is>
+          <t>Equivalent registered source series are joined across strictly non-overlapping validity windows.</t>
+        </is>
+      </c>
+      <c r="AV172" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr">
+        <is>
+          <t>official_csv_and_workbook</t>
+        </is>
+      </c>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>cda_weekly_bulletin</t>
+        </is>
+      </c>
+      <c r="BA172" t="inlineStr">
+        <is>
+          <t>Singapore CDA Weekly Infectious Diseases Bulletin</t>
+        </is>
+      </c>
+      <c r="BB172" t="inlineStr">
+        <is>
+          <t>https://www.cda.gov.sg/resources/weekly-infectious-diseases-bulletin-2026/</t>
+        </is>
+      </c>
+      <c r="BC172" t="inlineStr">
         <is>
           <t>official_csv_and_workbook</t>
         </is>
@@ -30722,7 +30867,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10">
@@ -30732,7 +30877,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>170</v>
+        <v>171</v>
       </c>
     </row>
     <row r="11">
@@ -30784,7 +30929,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21701</v>
+        <v>21721</v>
       </c>
     </row>
     <row r="16">

--- a/diseases/d011/2026-2029.xlsx
+++ b/diseases/d011/2026-2029.xlsx
@@ -56915,13 +56915,13 @@
         </is>
       </c>
       <c r="N314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O314" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="R314" t="n">
-        <v>0</v>
+        <v>0.03557618341728275</v>
       </c>
       <c r="S314" t="inlineStr">
         <is>
@@ -57074,10 +57074,10 @@
         </is>
       </c>
       <c r="N315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O315" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U315" t="inlineStr">
         <is>
@@ -57564,7 +57564,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>32416</v>
+        <v>32418</v>
       </c>
     </row>
     <row r="16">
